--- a/data/exports/key_account_intelligence.xlsx
+++ b/data/exports/key_account_intelligence.xlsx
@@ -449,7 +449,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>data_version 20261016T044819Z · 단위 억원(KRW) · 생성 2026-10-16T04:48:20.784667+00:00</t>
+          <t>data_version 20261016T051757Z · 단위 억원(KRW) · 생성 2026-10-16T05:17:59.039153+00:00</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>ESTIMATED</t>
+          <t>SCENARIO</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>ESTIMATED</t>
+          <t>SCENARIO</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EVIDENCE_VERIFIED</t>
+          <t>INPUTS_VERIFIED</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>EVIDENCE_VERIFIED</t>
+          <t>INPUTS_VERIFIED</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>EVIDENCE_VERIFIED</t>
+          <t>INPUTS_VERIFIED</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>EVIDENCE_VERIFIED</t>
+          <t>INPUTS_VERIFIED</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>EVIDENCE_VERIFIED</t>
+          <t>INPUTS_VERIFIED</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>EVIDENCE_VERIFIED</t>
+          <t>INPUTS_VERIFIED</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>EVIDENCE_VERIFIED</t>
+          <t>INPUTS_VERIFIED</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>EVIDENCE_VERIFIED</t>
+          <t>INPUTS_VERIFIED</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>ESTIMATED</t>
+          <t>SCENARIO</t>
         </is>
       </c>
       <c r="O39" t="n">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>ESTIMATED</t>
+          <t>SCENARIO</t>
         </is>
       </c>
       <c r="O46" t="n">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>EVIDENCE_VERIFIED</t>
+          <t>INPUTS_VERIFIED</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>EVIDENCE_VERIFIED</t>
+          <t>INPUTS_VERIFIED</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>EVIDENCE_VERIFIED</t>
+          <t>INPUTS_VERIFIED</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ESTIMATED</t>
+          <t>SCENARIO</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ESTIMATED</t>
+          <t>SCENARIO</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ESTIMATED</t>
+          <t>SCENARIO</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ESTIMATED</t>
+          <t>SCENARIO</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ESTIMATED</t>
+          <t>SCENARIO</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ESTIMATED</t>
+          <t>SCENARIO</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -16620,7 +16620,11 @@
           <t>FPR_2026 = Σ(RAW_i × Capture_Ceiling_i)  [C-CAP 2026]</t>
         </is>
       </c>
-      <c r="J221" t="inlineStr"/>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>KA32-E01, KA32-E03, KA32-P1-E01</t>
+        </is>
+      </c>
       <c r="K221" t="inlineStr">
         <is>
           <t>C-CAP</t>
@@ -18381,7 +18385,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>ESTIMATED</t>
+          <t>SCENARIO</t>
         </is>
       </c>
       <c r="H261" t="n">
@@ -18432,7 +18436,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>ESTIMATED</t>
+          <t>SCENARIO</t>
         </is>
       </c>
       <c r="H262" t="n">
@@ -18483,7 +18487,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>ESTIMATED</t>
+          <t>SCENARIO</t>
         </is>
       </c>
       <c r="H263" t="n">
@@ -20509,7 +20513,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>ESTIMATED</t>
+          <t>SCENARIO</t>
         </is>
       </c>
       <c r="H310" t="n">
@@ -20560,7 +20564,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>ESTIMATED</t>
+          <t>SCENARIO</t>
         </is>
       </c>
       <c r="H311" t="n">
@@ -20611,7 +20615,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>ESTIMATED</t>
+          <t>SCENARIO</t>
         </is>
       </c>
       <c r="H312" t="n">

--- a/data/exports/key_account_intelligence.xlsx
+++ b/data/exports/key_account_intelligence.xlsx
@@ -449,7 +449,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>data_version 20261016T051757Z · 단위 억원(KRW) · 생성 2026-10-16T05:17:59.039153+00:00</t>
+          <t>data_version 20261016T123435Z · 단위 억원(KRW) · 생성 2026-10-16T12:34:36.730335+00:00</t>
         </is>
       </c>
     </row>
